--- a/public/assets/template_import_data.xlsx
+++ b/public/assets/template_import_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ProjekBaru\kp_dela_hanggar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ProjekBaru\kp_dela_hanggar\new-app\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14443C9-2777-4C05-B4A2-4FE8B28C7E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFDDC99-83EB-4C08-8000-6CACBD4E32C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{89701FB7-334C-4B75-BA49-97D3FBFB9F77}"/>
+    <workbookView xWindow="6180" yWindow="2052" windowWidth="12504" windowHeight="6864" xr2:uid="{89701FB7-334C-4B75-BA49-97D3FBFB9F77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Nama</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>Gaji Pokok</t>
   </si>
 </sst>
 </file>
@@ -405,15 +408,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4607C766-3976-4789-9B09-477D9AEA3B1F}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
     <col min="5" max="5" width="16.5546875" customWidth="1"/>
     <col min="6" max="6" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,17 +436,20 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F5" s="1"/>
     </row>
   </sheetData>
